--- a/docs/testing/parts-import-fixtures/xlsx/parts-import-style-05.xlsx
+++ b/docs/testing/parts-import-fixtures/xlsx/parts-import-style-05.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="185">
   <si>
     <t>code</t>
   </si>
@@ -79,18 +79,12 @@
     <t>Leviton</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005002</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>F-05-003</t>
   </si>
   <si>
@@ -106,18 +100,12 @@
     <t>Minerallac</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005003</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>W-05-004</t>
   </si>
   <si>
@@ -133,9 +121,6 @@
     <t>Southwire</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005004</t>
   </si>
   <si>
@@ -160,9 +145,6 @@
     <t>Allied Tube</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005005</t>
   </si>
   <si>
@@ -187,18 +169,12 @@
     <t>Bridgeport</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005006</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-007</t>
   </si>
   <si>
@@ -214,18 +190,12 @@
     <t>Square D</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005007</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-008</t>
   </si>
   <si>
@@ -241,799 +211,358 @@
     <t>Raco</t>
   </si>
   <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005008</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>L-05-009</t>
   </si>
   <si>
-    <t>Lighting</t>
-  </si>
-  <si>
     <t>LED Flat Panel #2</t>
   </si>
   <si>
     <t>63.18</t>
   </si>
   <si>
-    <t>Lithonia</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005009</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>D-05-010</t>
   </si>
   <si>
-    <t>Devices</t>
-  </si>
-  <si>
     <t>Decorator Receptacle #3</t>
   </si>
   <si>
     <t>4.47</t>
   </si>
   <si>
-    <t>Leviton</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005010</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>F-05-011</t>
   </si>
   <si>
-    <t>Fasteners</t>
-  </si>
-  <si>
     <t>Strut Strap #4</t>
   </si>
   <si>
     <t>0.90</t>
   </si>
   <si>
-    <t>Minerallac</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005011</t>
   </si>
   <si>
     <t>36</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>W-05-012</t>
   </si>
   <si>
-    <t>Wire</t>
-  </si>
-  <si>
     <t>12 AWG THHN Copper Wire 500 ft spool</t>
   </si>
   <si>
     <t>0.27</t>
   </si>
   <si>
-    <t>Southwire</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005012</t>
   </si>
   <si>
     <t>39</t>
   </si>
   <si>
-    <t>ft</t>
-  </si>
-  <si>
     <t>C-05-013</t>
   </si>
   <si>
-    <t>Conduit</t>
-  </si>
-  <si>
     <t>1 in EMT Conduit 10 ft</t>
   </si>
   <si>
     <t>10.80</t>
   </si>
   <si>
-    <t>Allied Tube</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005013</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>stick</t>
-  </si>
-  <si>
     <t>F-05-014</t>
   </si>
   <si>
-    <t>Fittings</t>
-  </si>
-  <si>
     <t>EMT Set-Screw Connector #7</t>
   </si>
   <si>
     <t>1.42</t>
   </si>
   <si>
-    <t>Bridgeport</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005014</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-015</t>
   </si>
   <si>
-    <t>Breakers</t>
-  </si>
-  <si>
     <t>50A 1-pole QO Plug-On Breaker</t>
   </si>
   <si>
     <t>14.89</t>
   </si>
   <si>
-    <t>Square D</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005015</t>
   </si>
   <si>
     <t>48</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-016</t>
   </si>
   <si>
-    <t>Boxes</t>
-  </si>
-  <si>
     <t>Steel Device Box #9</t>
   </si>
   <si>
     <t>3.39</t>
   </si>
   <si>
-    <t>Raco</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005016</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>L-05-017</t>
   </si>
   <si>
-    <t>Lighting</t>
-  </si>
-  <si>
     <t>LED Flat Panel #10</t>
   </si>
   <si>
     <t>59.54</t>
   </si>
   <si>
-    <t>Lithonia</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005017</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>D-05-018</t>
   </si>
   <si>
-    <t>Devices</t>
-  </si>
-  <si>
     <t>Decorator Receptacle #11</t>
   </si>
   <si>
     <t>4.23</t>
   </si>
   <si>
-    <t>Leviton</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005018</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>F-05-019</t>
   </si>
   <si>
-    <t>Fasteners</t>
-  </si>
-  <si>
     <t>Strut Strap #12</t>
   </si>
   <si>
     <t>0.85</t>
   </si>
   <si>
-    <t>Minerallac</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005019</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>W-05-020</t>
   </si>
   <si>
-    <t>Wire</t>
-  </si>
-  <si>
     <t>6 AWG THHN Copper Wire 500 ft spool</t>
   </si>
   <si>
     <t>0.26</t>
   </si>
   <si>
-    <t>Southwire</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005020</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
     <t>C-05-021</t>
   </si>
   <si>
-    <t>Conduit</t>
-  </si>
-  <si>
     <t>1/2 in EMT Conduit 10 ft</t>
   </si>
   <si>
     <t>10.29</t>
   </si>
   <si>
-    <t>Allied Tube</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005021</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>stick</t>
-  </si>
-  <si>
     <t>F-05-022</t>
   </si>
   <si>
-    <t>Fittings</t>
-  </si>
-  <si>
     <t>EMT Set-Screw Connector #3</t>
   </si>
   <si>
     <t>2.27</t>
   </si>
   <si>
-    <t>Bridgeport</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005022</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-023</t>
   </si>
   <si>
-    <t>Breakers</t>
-  </si>
-  <si>
     <t>30A 1-pole QO Plug-On Breaker</t>
   </si>
   <si>
     <t>13.85</t>
   </si>
   <si>
-    <t>Square D</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005023</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-024</t>
   </si>
   <si>
-    <t>Boxes</t>
-  </si>
-  <si>
     <t>Steel Device Box #5</t>
   </si>
   <si>
     <t>3.17</t>
   </si>
   <si>
-    <t>Raco</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005024</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>L-05-025</t>
   </si>
   <si>
-    <t>Lighting</t>
-  </si>
-  <si>
-    <t>LED Flat Panel #6</t>
-  </si>
-  <si>
     <t>55.89</t>
   </si>
   <si>
-    <t>Lithonia</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005025</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>D-05-026</t>
   </si>
   <si>
-    <t>Devices</t>
-  </si>
-  <si>
-    <t>Decorator Receptacle #7</t>
-  </si>
-  <si>
     <t>3.98</t>
   </si>
   <si>
-    <t>Leviton</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005026</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>F-05-027</t>
   </si>
   <si>
-    <t>Fasteners</t>
-  </si>
-  <si>
-    <t>Strut Strap #8</t>
-  </si>
-  <si>
     <t>0.81</t>
   </si>
   <si>
-    <t>Minerallac</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005027</t>
   </si>
   <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>W-05-028</t>
   </si>
   <si>
-    <t>Wire</t>
-  </si>
-  <si>
     <t>10 AWG THHN Copper Wire 500 ft spool</t>
   </si>
   <si>
     <t>0.25</t>
   </si>
   <si>
-    <t>Southwire</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005028</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
     <t>C-05-029</t>
   </si>
   <si>
-    <t>Conduit</t>
-  </si>
-  <si>
     <t>1-1/4 in EMT Conduit 10 ft</t>
   </si>
   <si>
     <t>9.79</t>
   </si>
   <si>
-    <t>Allied Tube</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005029</t>
   </si>
   <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>stick</t>
-  </si>
-  <si>
     <t>F-05-030</t>
   </si>
   <si>
-    <t>Fittings</t>
-  </si>
-  <si>
-    <t>EMT Set-Screw Connector #11</t>
-  </si>
-  <si>
     <t>2.17</t>
   </si>
   <si>
-    <t>Bridgeport</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005030</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-031</t>
   </si>
   <si>
-    <t>Breakers</t>
-  </si>
-  <si>
     <t>15A 1-pole QO Plug-On Breaker</t>
   </si>
   <si>
     <t>22.16</t>
   </si>
   <si>
-    <t>Square D</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005031</t>
   </si>
   <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>B-05-032</t>
   </si>
   <si>
-    <t>Boxes</t>
-  </si>
-  <si>
-    <t>Steel Device Box #1</t>
-  </si>
-  <si>
     <t>2.95</t>
   </si>
   <si>
-    <t>Raco</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005032</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>L-05-033</t>
   </si>
   <si>
-    <t>Lighting</t>
-  </si>
-  <si>
-    <t>LED Flat Panel #2</t>
-  </si>
-  <si>
     <t>52.24</t>
   </si>
   <si>
-    <t>Lithonia</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005033</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>D-05-034</t>
   </si>
   <si>
-    <t>Devices</t>
-  </si>
-  <si>
-    <t>Decorator Receptacle #3</t>
-  </si>
-  <si>
     <t>3.74</t>
   </si>
   <si>
-    <t>Leviton</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005034</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>F-05-035</t>
   </si>
   <si>
-    <t>Fasteners</t>
-  </si>
-  <si>
-    <t>Strut Strap #4</t>
-  </si>
-  <si>
     <t>0.76</t>
   </si>
   <si>
-    <t>Minerallac</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005035</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>ea</t>
-  </si>
-  <si>
     <t>W-05-036</t>
   </si>
   <si>
-    <t>Wire</t>
-  </si>
-  <si>
     <t>14 AWG THHN Copper Wire 500 ft spool</t>
   </si>
   <si>
     <t>0.23</t>
   </si>
   <si>
-    <t>Southwire</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005036</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
     <t>C-05-037</t>
   </si>
   <si>
-    <t>Conduit</t>
-  </si>
-  <si>
     <t>3/4 in EMT Conduit 10 ft</t>
   </si>
   <si>
     <t>9.28</t>
   </si>
   <si>
-    <t>Allied Tube</t>
-  </si>
-  <si>
-    <t>Jobsite Stock Recount</t>
-  </si>
-  <si>
     <t>880000005037</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>stick</t>
   </si>
 </sst>
 </file>
@@ -1075,28 +604,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>227</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1104,1043 +633,1043 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
-        <v>313</v>
-      </c>
       <c r="I3" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
         <v>27</v>
       </c>
-      <c r="B4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" t="s">
-        <v>245</v>
-      </c>
       <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
-        <v>319</v>
-      </c>
-      <c r="F4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
       <c r="H4" t="s">
-        <v>322</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
-        <v>325</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" t="s">
+      <c r="I5" t="s">
         <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>328</v>
-      </c>
-      <c r="F5" t="s">
-        <v>338</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" t="s">
-        <v>331</v>
-      </c>
-      <c r="I5" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="H6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" t="s">
         <v>47</v>
-      </c>
-      <c r="D6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" t="s">
-        <v>337</v>
-      </c>
-      <c r="F6" t="s">
-        <v>338</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6" t="s">
-        <v>340</v>
-      </c>
-      <c r="I6" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" t="s">
         <v>54</v>
       </c>
-      <c r="B7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" t="s">
-        <v>272</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>274</v>
-      </c>
-      <c r="F7" t="s">
-        <v>338</v>
-      </c>
-      <c r="G7" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" t="s">
-        <v>205</v>
-      </c>
       <c r="I7" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="I9" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>299</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="H10" t="s">
-        <v>232</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>259</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>268</v>
+        <v>93</v>
       </c>
       <c r="I14" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="E15" t="s">
-        <v>274</v>
+        <v>52</v>
       </c>
       <c r="F15" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="B16" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E16" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="F16" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="H16" t="s">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="B17" t="s">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="F17" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="H17" t="s">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>313</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="H20" t="s">
-        <v>322</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="C22" t="s">
-        <v>191</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="E22" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="F22" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>195</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>340</v>
+        <v>46</v>
       </c>
       <c r="I22" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="H23" t="s">
-        <v>205</v>
+        <v>54</v>
       </c>
       <c r="I23" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="F24" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>213</v>
+        <v>136</v>
       </c>
       <c r="H24" t="s">
-        <v>214</v>
+        <v>61</v>
       </c>
       <c r="I24" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>218</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>219</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="F25" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>140</v>
       </c>
       <c r="H25" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="I25" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>225</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>227</v>
+        <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="H26" t="s">
-        <v>232</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>234</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
-        <v>236</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
       <c r="H27" t="s">
-        <v>241</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>243</v>
+        <v>147</v>
       </c>
       <c r="B28" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>148</v>
       </c>
       <c r="E28" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="F28" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>249</v>
+        <v>149</v>
       </c>
       <c r="H28" t="s">
-        <v>250</v>
+        <v>83</v>
       </c>
       <c r="I28" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>252</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="D29" t="s">
-        <v>255</v>
+        <v>152</v>
       </c>
       <c r="E29" t="s">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>258</v>
+        <v>153</v>
       </c>
       <c r="H29" t="s">
-        <v>259</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="B30" t="s">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>263</v>
+        <v>155</v>
       </c>
       <c r="D30" t="s">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="E30" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>267</v>
+        <v>157</v>
       </c>
       <c r="H30" t="s">
-        <v>268</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>50</v>
       </c>
       <c r="D31" t="s">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>274</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>276</v>
+        <v>160</v>
       </c>
       <c r="H31" t="s">
-        <v>277</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>279</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>281</v>
+        <v>162</v>
       </c>
       <c r="D32" t="s">
-        <v>282</v>
+        <v>163</v>
       </c>
       <c r="E32" t="s">
-        <v>283</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>285</v>
+        <v>164</v>
       </c>
       <c r="H32" t="s">
-        <v>286</v>
+        <v>103</v>
       </c>
       <c r="I32" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>288</v>
+        <v>165</v>
       </c>
       <c r="B33" t="s">
-        <v>289</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>290</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
-        <v>292</v>
+        <v>66</v>
       </c>
       <c r="F33" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>294</v>
+        <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="I33" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>297</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>299</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>300</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>301</v>
+        <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>303</v>
+        <v>170</v>
       </c>
       <c r="H34" t="s">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c r="I34" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="B35" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>309</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F35" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>312</v>
+        <v>173</v>
       </c>
       <c r="H35" t="s">
-        <v>313</v>
+        <v>24</v>
       </c>
       <c r="I35" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>316</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>317</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
-        <v>318</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>319</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>321</v>
+        <v>176</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>31</v>
       </c>
       <c r="I36" t="s">
-        <v>323</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>325</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>326</v>
+        <v>178</v>
       </c>
       <c r="D37" t="s">
-        <v>327</v>
+        <v>179</v>
       </c>
       <c r="E37" t="s">
-        <v>328</v>
+        <v>36</v>
       </c>
       <c r="F37" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>330</v>
+        <v>180</v>
       </c>
       <c r="H37" t="s">
-        <v>331</v>
+        <v>38</v>
       </c>
       <c r="I37" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>335</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>336</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>337</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>338</v>
+        <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>339</v>
+        <v>184</v>
       </c>
       <c r="H38" t="s">
-        <v>340</v>
+        <v>46</v>
       </c>
       <c r="I38" t="s">
-        <v>341</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
